--- a/docs/3. brainstorm/Варианты хранения данных.xlsx
+++ b/docs/3. brainstorm/Варианты хранения данных.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\_ii_\reference_data\docs\3. brainstorm\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5005F981-E806-4983-8150-591299A89F9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D322E6BF-DBCA-46FA-B291-52CC031FA1ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8055" yWindow="2880" windowWidth="21600" windowHeight="11295" xr2:uid="{6A6E01FB-E36E-44DF-A74E-69A8D2AAC69B}"/>
+    <workbookView xWindow="3300" yWindow="3225" windowWidth="21600" windowHeight="11295" xr2:uid="{6A6E01FB-E36E-44DF-A74E-69A8D2AAC69B}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1 (2)" sheetId="2" r:id="rId1"/>
@@ -242,107 +242,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E5" authorId="0" shapeId="0" xr:uid="{123619F4-EB9A-43DC-8C91-0097D302A2AD}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="204"/>
-          </rPr>
-          <t>Антон Касперович:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="204"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="204"/>
-          </rPr>
-          <t>Особенности</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="204"/>
-          </rPr>
-          <t xml:space="preserve">:
-+ Смысл Jsonb = динамическая структура
-+ Нет прямых ссылок. Вместо FK будет код родителя в текущей таблице и дата, на которую надо найти валидное значение кода. 
-+ Секционирование для разделения справочников друг от друга на 1 таблице 
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="204"/>
-          </rPr>
-          <t>Хорошо</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="204"/>
-          </rPr>
-          <t xml:space="preserve">: 
-+ Создание / изменение метаданных без SQL 
-+ Поиск (без FK) - быстрый
-+ Размер таблицы - минимальный (отсутствие избыточного дублирования)
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="204"/>
-          </rPr>
-          <t>Плохо</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="204"/>
-          </rPr>
-          <t xml:space="preserve">:
-- Валидация полей - нет
-- Поиск (с FK) - медленный
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E6" authorId="0" shapeId="0" xr:uid="{E9AD7EB8-37E4-40A3-9FE1-A59656896141}">
+    <comment ref="E5" authorId="0" shapeId="0" xr:uid="{E9AD7EB8-37E4-40A3-9FE1-A59656896141}">
       <text>
         <r>
           <rPr>
@@ -441,6 +341,106 @@
 - Поиск по историческим данных (без FK) - медленный
 - Поиск по историческим данных (с FK) - медленный
 - Размер таблицы - большой (много избыточного дублирования)
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E6" authorId="0" shapeId="0" xr:uid="{123619F4-EB9A-43DC-8C91-0097D302A2AD}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Антон Касперович:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Особенности</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">:
++ Смысл Jsonb = динамическая структура
++ Нет прямых ссылок. Вместо FK будет код родителя в текущей таблице и дата, на которую надо найти валидное значение кода. 
++ Секционирование для разделения справочников друг от друга на 1 таблице 
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Хорошо</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">: 
++ Создание / изменение метаданных без SQL 
++ Поиск (без FK) - быстрый
++ Размер таблицы - минимальный (отсутствие избыточного дублирования)
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Плохо</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">:
+- Валидация полей - нет
+- Поиск (с FK) - медленный
 </t>
         </r>
       </text>
@@ -450,7 +450,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="25">
   <si>
     <t>Число таблиц</t>
   </si>
@@ -525,6 +525,9 @@
   <si>
     <t>Стандартный AS IS
 + Подзарпос: Код + Дата</t>
+  </si>
+  <si>
+    <t>№</t>
   </si>
 </sst>
 </file>
@@ -930,7 +933,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2C5CB3C-29F3-415E-8A76-DD351AC242EF}">
-  <dimension ref="B2:E6"/>
+  <dimension ref="A2:E6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="27.140625" bestFit="1" customWidth="1"/>
@@ -939,7 +942,10 @@
     <col min="5" max="5" width="17.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -953,7 +959,10 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>1</v>
+      </c>
       <c r="B3" t="s">
         <v>5</v>
       </c>
@@ -967,7 +976,10 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>2</v>
+      </c>
       <c r="B4" t="s">
         <v>5</v>
       </c>
@@ -981,32 +993,38 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
+    <row r="5" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
         <v>14</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C6" t="s">
         <v>19</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D6" t="s">
         <v>16</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E6" t="s">
         <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="2:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="B6" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" t="s">
-        <v>12</v>
       </c>
     </row>
   </sheetData>
